--- a/naver-place-crawler/results_health/대구_PT.xlsx
+++ b/naver-place-crawler/results_health/대구_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 중구 이천로 204-1 5층</t>
+          <t>대구 중구 이천로 204-1 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sh6l</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -624,10 +628,10 @@
         <v>113</v>
       </c>
       <c r="Q2" t="n">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="R2" t="n">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 동구점</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>catess110@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1493-7680</t>
+          <t>0507-1356-4013</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 동구 안심로 266 4층</t>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/catess110</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>757</v>
+        <v>104</v>
       </c>
       <c r="Q3" t="n">
-        <v>1310</v>
+        <v>328</v>
       </c>
       <c r="R3" t="n">
-        <v>2067</v>
+        <v>432</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>77223878</t>
+          <t>1701902663</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/77223878</t>
+          <t>https://m.place.naver.com/place/1701902663</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 대구점</t>
+          <t>바디엔지니어스짐 동구점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>l860923l@naver.com</t>
+          <t>catess110@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1356-4013</t>
+          <t>0507-1493-7680</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
+          <t>대구 동구 안심로 266 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems2</t>
+          <t>https://blog.naver.com/catess110</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,19 +797,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r5eg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>104</v>
+        <v>757</v>
       </c>
       <c r="Q4" t="n">
-        <v>327</v>
+        <v>1310</v>
       </c>
       <c r="R4" t="n">
-        <v>431</v>
+        <v>2067</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1701902663</t>
+          <t>77223878</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701902663</t>
+          <t>https://m.place.naver.com/place/77223878</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -845,34 +849,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>플랜PT샵</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>dnwls6050@naver.com</t>
-        </is>
-      </c>
+          <t>빡짐 헬스 P.T&amp;G.X</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1439-8242</t>
+          <t>0507-1394-8342</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 북구 학정로 430 3층 304 305호</t>
+          <t>대구 달서구 진천로 72 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dnwls6050</t>
+          <t>https://www.instagram.com/ppark_gym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuz9732</t>
+          <t>https://talk.naver.com/ct/w6cut0e</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="Q5" t="n">
-        <v>231</v>
+        <v>32</v>
       </c>
       <c r="R5" t="n">
-        <v>334</v>
+        <v>65</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1053211445</t>
+          <t>1349138451</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053211445</t>
+          <t>https://m.place.naver.com/place/1349138451</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -943,30 +943,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>빡짐 헬스 P.T&amp;G.X</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>플랜PT샵</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dnwls6050@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1394-8342</t>
+          <t>0507-1439-8242</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 달서구 진천로 72 4층</t>
+          <t>대구 북구 학정로 430 3층 304 305호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ppark_gym</t>
+          <t>https://blog.naver.com/dnwls6050</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -981,15 +985,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wuz9732</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>231</v>
       </c>
       <c r="R6" t="n">
-        <v>65</v>
+        <v>334</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1349138451</t>
+          <t>1053211445</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349138451</t>
+          <t>https://m.place.naver.com/place/1053211445</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1055,7 +1063,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 중구 공평로8길 11-1 3층</t>
+          <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1080,10 +1088,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r74y</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1098,10 +1110,10 @@
         <v>409</v>
       </c>
       <c r="Q7" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="R7" t="n">
-        <v>2422</v>
+        <v>2430</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1149,7 +1161,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1174,10 +1186,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9se</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1192,10 +1208,10 @@
         <v>697</v>
       </c>
       <c r="Q8" t="n">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="R8" t="n">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1243,7 +1259,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
+          <t>대구 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wtum</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1283,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="Q9" t="n">
         <v>173</v>
       </c>
       <c r="R9" t="n">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1320,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>인더짐 헬스&amp;요가&amp;필라테스&amp;줌바&amp;PT 죽전점</t>
+          <t>헬스&amp;PT 몰리짐 장기점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>inthegym04@naver.com</t>
+          <t>mollygym_vol3@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1312-8611</t>
+          <t>0507-1469-9682</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 달서구 달구벌대로 1530 2층 201~205, 211~212호</t>
+          <t>대구 달서구 용산로 80 에이동</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/inthegym04</t>
+          <t>https://www.instagram.com/mollygym_vol.3/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,15 +1377,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t9mv</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>203</v>
+        <v>989</v>
       </c>
       <c r="Q10" t="n">
-        <v>335</v>
+        <v>539</v>
       </c>
       <c r="R10" t="n">
-        <v>538</v>
+        <v>1528</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1896860278</t>
+          <t>1048460846</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1896860278</t>
+          <t>https://m.place.naver.com/place/1048460846</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유케이 짐</t>
+          <t>인더짐 헬스&amp;요가&amp;필라테스&amp;줌바&amp;PT 죽전점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ukgym_official@naver.com</t>
+          <t>inthegym04@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1399-1895</t>
+          <t>0507-1312-8611</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 달서구 달구벌대로309길 13 지하1층</t>
+          <t>대구 달서구 달구벌대로 1530 2층 201~205, 211~212호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ukgym_official</t>
+          <t>https://blog.naver.com/inthegym04</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1456,10 +1480,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5im8a</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1471,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="Q11" t="n">
-        <v>131</v>
+        <v>335</v>
       </c>
       <c r="R11" t="n">
-        <v>364</v>
+        <v>538</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1054343439</t>
+          <t>1896860278</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054343439</t>
+          <t>https://m.place.naver.com/place/1896860278</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/대구_PT.xlsx
+++ b/naver-place-crawler/results_health/대구_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 대구점</t>
+          <t>비비웰니스 클럽 Wellness PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>l860923l@naver.com</t>
+          <t>bbwellness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1356-4013</t>
+          <t>0507-1400-9891</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
+          <t>대구 중구 이천로 204-1 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems2</t>
+          <t>https://blog.naver.com/bbwellness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r5eg</t>
+          <t>https://talk.naver.com/ct/w4sh6l</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="Q2" t="n">
-        <v>329</v>
+        <v>639</v>
       </c>
       <c r="R2" t="n">
-        <v>432</v>
+        <v>752</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1701902663</t>
+          <t>1417211379</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701902663</t>
+          <t>https://m.place.naver.com/place/1417211379</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 동구점</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>catess110@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1493-7680</t>
+          <t>0507-1356-4013</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 동구 안심로 266 4층</t>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/catess110</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>767</v>
+        <v>103</v>
       </c>
       <c r="Q3" t="n">
-        <v>1313</v>
+        <v>329</v>
       </c>
       <c r="R3" t="n">
-        <v>2080</v>
+        <v>432</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>77223878</t>
+          <t>1701902663</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/77223878</t>
+          <t>https://m.place.naver.com/place/1701902663</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -751,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>플랜PT샵</t>
+          <t>바디엔지니어스짐 동구점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dnwls6050@naver.com</t>
+          <t>catess110@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1439-8242</t>
+          <t>0507-1493-7680</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 북구 학정로 430 3층 304 305호</t>
+          <t>대구 동구 안심로 266 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dnwls6050</t>
+          <t>https://blog.naver.com/catess110</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -798,14 +802,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wuz9732</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>106</v>
+        <v>767</v>
       </c>
       <c r="Q4" t="n">
-        <v>235</v>
+        <v>1313</v>
       </c>
       <c r="R4" t="n">
-        <v>341</v>
+        <v>2080</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1053211445</t>
+          <t>77223878</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053211445</t>
+          <t>https://m.place.naver.com/place/77223878</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>워너비핏</t>
+          <t>플랜PT샵</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wannabefit2400@naver.com</t>
+          <t>dnwls6050@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1407-2402</t>
+          <t>0507-1439-8242</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 달구벌대로 2317 . 105동 지하1층 비1호(수성동4 가, 우방사랑마을아파트)</t>
+          <t>대구 북구 학정로 430 3층 304 305호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wannabefit2400</t>
+          <t>https://blog.naver.com/dnwls6050</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wuz9732</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="Q5" t="n">
-        <v>123</v>
+        <v>235</v>
       </c>
       <c r="R5" t="n">
-        <v>248</v>
+        <v>341</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1742130217</t>
+          <t>1053211445</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742130217</t>
+          <t>https://m.place.naver.com/place/1053211445</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -965,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 중구 공평로8길 11-1 3층</t>
+          <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -990,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r74y</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1008,10 +1016,10 @@
         <v>420</v>
       </c>
       <c r="Q6" t="n">
-        <v>2105</v>
+        <v>2110</v>
       </c>
       <c r="R6" t="n">
-        <v>2525</v>
+        <v>2530</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1059,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 달서구 용산로 80 에이동</t>
+          <t>대구 달서구 용산로 80 에이동</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1084,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t9mv</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1099,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="Q7" t="n">
         <v>545</v>
       </c>
       <c r="R7" t="n">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1153,7 +1165,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1178,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9se</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1196,10 +1212,10 @@
         <v>700</v>
       </c>
       <c r="Q8" t="n">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="R8" t="n">
-        <v>1720</v>
+        <v>1723</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1247,7 +1263,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
+          <t>대구 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1272,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wtum</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1290,10 +1310,10 @@
         <v>714</v>
       </c>
       <c r="Q9" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R9" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1341,7 +1361,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 용학로25안길 9 세종빌딩 2층</t>
+          <t>대구 수성구 용학로25안길 9 세종빌딩 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1366,10 +1386,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eysk</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1503,96 +1527,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>국민피티 월배점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>kukminptwolbae@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>대구광역시 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/kukminptwolbae</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>184</v>
-      </c>
-      <c r="R12" t="n">
-        <v>211</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1009333460</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1009333460</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/대구_PT.xlsx
+++ b/naver-place-crawler/results_health/대구_PT.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구 중구 이천로 204-1 5층</t>
+          <t>대구광역시 중구 이천로 204-1 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sh6l</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -628,10 +624,10 @@
         <v>113</v>
       </c>
       <c r="Q2" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R2" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -777,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 동구 안심로 266 4층</t>
+          <t>대구광역시 동구 안심로 266 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -969,7 +965,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구 중구 공평로8길 11-1 3층</t>
+          <t>대구광역시 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +990,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r74y</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1016,10 +1008,10 @@
         <v>420</v>
       </c>
       <c r="Q6" t="n">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="R6" t="n">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1067,7 +1059,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구 달서구 용산로 80 에이동</t>
+          <t>대구광역시 달서구 용산로 80 에이동</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1092,14 +1084,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5t9mv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1065</v>
+        <v>1077</v>
       </c>
       <c r="Q7" t="n">
         <v>545</v>
       </c>
       <c r="R7" t="n">
-        <v>1610</v>
+        <v>1622</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1165,7 +1153,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,14 +1178,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f9se</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1212,10 +1196,10 @@
         <v>700</v>
       </c>
       <c r="Q8" t="n">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="R8" t="n">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1263,7 +1247,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 북구 동북로 244 BL타워 13층</t>
+          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1288,14 +1272,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wtum</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1307,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Q9" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R9" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1344,29 +1324,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>클린짐 포레스트점 헬스&amp;P.T</t>
+          <t>TREX트레이닝센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hell12311@naver.com</t>
+          <t>trex211@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1399-4477</t>
+          <t>053-744-0405</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 수성구 용학로25안길 9 세종빌딩 2층</t>
+          <t>대구광역시 수성구 동대구로 389 동방빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://youtube.com/@클린짐</t>
+          <t>https://www.youtube.com/channel/UCoIsLH8DW0KTkldy4KtyyEw</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,14 +1366,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4eysk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>252</v>
+        <v>61</v>
       </c>
       <c r="Q10" t="n">
-        <v>214</v>
+        <v>1135</v>
       </c>
       <c r="R10" t="n">
-        <v>466</v>
+        <v>1196</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1016045083</t>
+          <t>82375205</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016045083</t>
+          <t>https://m.place.naver.com/place/82375205</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/대구_PT.xlsx
+++ b/naver-place-crawler/results_health/대구_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 중구 이천로 204-1 5층</t>
+          <t>대구 중구 이천로 204-1 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sh6l</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -773,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 동구 안심로 266 4층</t>
+          <t>대구 동구 안심로 266 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 중구 공평로8길 11-1 3층</t>
+          <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -990,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r74y</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1059,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 달서구 용산로 80 에이동</t>
+          <t>대구 달서구 용산로 80 에이동</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1084,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t9mv</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1099,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="Q7" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="R7" t="n">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1153,7 +1165,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1178,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9se</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1247,7 +1263,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
+          <t>대구 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1272,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wtum</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1290,10 +1310,10 @@
         <v>715</v>
       </c>
       <c r="Q9" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R9" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1341,7 +1361,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 동대구로 389 동방빌딩 3층</t>
+          <t>대구 수성구 동대구로 389 동방빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1418,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WR웰니스짐 수성 헬스&amp;PT</t>
+          <t>위즈고 헬스&amp;PT 시지점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wr_premium_fit@naver.com</t>
+          <t>woojung4545@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1386-9688</t>
+          <t>0507-1305-6676</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 수성구 동대구로 44 2층</t>
+          <t>대구 수성구 신매로19길 56 4층 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wr_premium_fit</t>
+          <t>https://blog.naver.com/woojung4545</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1465,27 +1485,27 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4d3lf</t>
+          <t>https://talk.naver.com/ct/wmrepxn</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>304</v>
+        <v>389</v>
       </c>
       <c r="Q11" t="n">
-        <v>731</v>
+        <v>330</v>
       </c>
       <c r="R11" t="n">
-        <v>1035</v>
+        <v>719</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,15 +1514,211 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1407080934</t>
+          <t>1586786552</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407080934</t>
+          <t>https://m.place.naver.com/place/1586786552</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>피크짐 신천점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>peakgym2022@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1355-6339</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대구 동구 장등로 66 1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/peakgym2022</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9noycr</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>488</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>62</v>
+      </c>
+      <c r="R12" t="n">
+        <v>550</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1934353498</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1934353498</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>엠엠짐 PT &amp; 교정 컨디셔닝 범어점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mm_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>053-744-0757</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>대구 수성구 달구벌대로480길 27 3층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mm_gym</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w448jf</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>35</v>
+      </c>
+      <c r="R13" t="n">
+        <v>103</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1219404715</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1219404715</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/대구_PT.xlsx
+++ b/naver-place-crawler/results_health/대구_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -748,41 +748,41 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 동구점</t>
+          <t>플랜PT샵</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>catess110@naver.com</t>
+          <t>dnwls6050@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1493-7680</t>
+          <t>0507-1439-8242</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 동구 안심로 266 4층</t>
+          <t>대구 북구 학정로 430 3층 304 305호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/catess110</t>
+          <t>https://blog.naver.com/dnwls6050</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wuz9732</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>767</v>
+        <v>106</v>
       </c>
       <c r="Q4" t="n">
-        <v>1313</v>
+        <v>235</v>
       </c>
       <c r="R4" t="n">
-        <v>2080</v>
+        <v>341</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>77223878</t>
+          <t>1053211445</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/77223878</t>
+          <t>https://m.place.naver.com/place/1053211445</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -854,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>플랜PT샵</t>
+          <t>워너비핏</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dnwls6050@naver.com</t>
+          <t>wannabefit2400@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1439-8242</t>
+          <t>0507-1407-2402</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 북구 학정로 430 3층 304 305호</t>
+          <t>대구 수성구 달구벌대로 2317 . 105동 지하1층 비1호(수성동4 가, 우방사랑마을아파트)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dnwls6050</t>
+          <t>https://blog.naver.com/wannabefit2400</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuz9732</t>
+          <t>https://talk.naver.com/ct/w40ykq</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="Q5" t="n">
-        <v>235</v>
+        <v>123</v>
       </c>
       <c r="R5" t="n">
-        <v>341</v>
+        <v>249</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1053211445</t>
+          <t>1742130217</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053211445</t>
+          <t>https://m.place.naver.com/place/1742130217</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1016,10 +1020,10 @@
         <v>420</v>
       </c>
       <c r="Q6" t="n">
-        <v>2112</v>
+        <v>2120</v>
       </c>
       <c r="R6" t="n">
-        <v>2532</v>
+        <v>2540</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1212,10 +1216,10 @@
         <v>700</v>
       </c>
       <c r="Q8" t="n">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="R8" t="n">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1375,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1426,7 +1430,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1438,29 +1442,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>위즈고 헬스&amp;PT 시지점</t>
+          <t>국민피티 월배점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>woojung4545@naver.com</t>
+          <t>kukminptwolbae@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1305-6676</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 수성구 신매로19길 56 4층 5층</t>
+          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woojung4545</t>
+          <t>https://blog.naver.com/kukminptwolbae</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,32 +1480,28 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wmrepxn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>389</v>
+        <v>27</v>
       </c>
       <c r="Q11" t="n">
-        <v>330</v>
+        <v>184</v>
       </c>
       <c r="R11" t="n">
-        <v>719</v>
+        <v>211</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1586786552</t>
+          <t>1009333460</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1586786552</t>
+          <t>https://m.place.naver.com/place/1009333460</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1536,29 +1532,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>피크짐 신천점</t>
+          <t>위즈고 헬스&amp;PT 시지점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>peakgym2022@naver.com</t>
+          <t>woojung4545@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1355-6339</t>
+          <t>0507-1305-6676</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구 동구 장등로 66 1층</t>
+          <t>대구 수성구 신매로19길 56 4층 5층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/peakgym2022</t>
+          <t>https://blog.naver.com/woojung4545</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1583,12 +1579,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9noycr</t>
+          <t>https://talk.naver.com/ct/wmrepxn</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1597,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>488</v>
+        <v>389</v>
       </c>
       <c r="Q12" t="n">
-        <v>62</v>
+        <v>330</v>
       </c>
       <c r="R12" t="n">
-        <v>550</v>
+        <v>719</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,115 +1608,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1934353498</t>
+          <t>1586786552</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1934353498</t>
+          <t>https://m.place.naver.com/place/1586786552</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>엠엠짐 PT &amp; 교정 컨디셔닝 범어점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>mm_gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>053-744-0757</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>대구 수성구 달구벌대로480길 27 3층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/mm_gym</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w448jf</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>35</v>
-      </c>
-      <c r="R13" t="n">
-        <v>103</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1219404715</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1219404715</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대구_PT.xlsx
+++ b/naver-place-crawler/results_health/대구_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bbwellness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dnwls6050</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wannabefit2400</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1020,10 +1020,10 @@
         <v>420</v>
       </c>
       <c r="Q6" t="n">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="R6" t="n">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mollygym_vol.3/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1152,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>국민피티 침산점</t>
+          <t>스톤짐 복현점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kukminpt@naver.com</t>
+          <t>stonegym_3@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1398-9797</t>
+          <t>0507-1333-5469</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kukminpt</t>
+          <t>http://pf.kakao.com/_pQdrxj</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4f9se</t>
+          <t>https://talk.naver.com/ct/w5wtum</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="Q8" t="n">
-        <v>1023</v>
+        <v>180</v>
       </c>
       <c r="R8" t="n">
-        <v>1723</v>
+        <v>895</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1636758988</t>
+          <t>1113466448</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636758988</t>
+          <t>https://m.place.naver.com/place/1113466448</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스톤짐 복현점</t>
+          <t>국민피티 침산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>stonegym_3@naver.com</t>
+          <t>kukminpt@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1333-5469</t>
+          <t>0507-1398-9797</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 북구 동북로 244 BL타워 13층</t>
+          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pQdrxj</t>
+          <t>https://www.instagram.com/kukminpt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wtum</t>
+          <t>https://talk.naver.com/ct/w4f9se</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="Q9" t="n">
-        <v>180</v>
+        <v>1022</v>
       </c>
       <c r="R9" t="n">
-        <v>895</v>
+        <v>1722</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1113466448</t>
+          <t>1636758988</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113466448</t>
+          <t>https://m.place.naver.com/place/1636758988</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,39 +1348,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TREX트레이닝센터</t>
+          <t>클린짐 포레스트점 헬스&amp;P.T</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>trex211@naver.com</t>
+          <t>hell12311@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>053-744-0405</t>
+          <t>0507-1399-4477</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 수성구 동대구로 389 동방빌딩 3층</t>
+          <t>대구 수성구 용학로25안길 9 세종빌딩 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCoIsLH8DW0KTkldy4KtyyEw</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1390,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eysk</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>61</v>
+        <v>252</v>
       </c>
       <c r="Q10" t="n">
-        <v>1135</v>
+        <v>215</v>
       </c>
       <c r="R10" t="n">
-        <v>1196</v>
+        <v>467</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>82375205</t>
+          <t>1016045083</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/82375205</t>
+          <t>https://m.place.naver.com/place/1016045083</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1527,96 +1531,292 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>위즈고 헬스&amp;PT 시지점</t>
+          <t>헬핏 뉴로트레이닝 &amp; 재활PT 범어점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>woojung4545@naver.com</t>
+          <t>helfit@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1305-6676</t>
+          <t>0507-1471-6364</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>대구 수성구 청호로95길 23 3층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/helfit</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5sppd2</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>40</v>
+      </c>
+      <c r="R12" t="n">
+        <v>61</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1467150211</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1467150211</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>비무브짐24 헬스&amp;PT 상인점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>skyseung2@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1469-7950</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>대구 달서구 월곡로 219 4층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i8k0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>964</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>300</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1264</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1215597139</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1215597139</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>위즈고 헬스&amp;PT 시지점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hanyang0226@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1305-6676</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>대구 수성구 신매로19길 56 4층 5층</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/woojung4545</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/wmrepxn</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>389</v>
       </c>
-      <c r="Q12" t="n">
-        <v>330</v>
-      </c>
-      <c r="R12" t="n">
-        <v>719</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="Q14" t="n">
+        <v>331</v>
+      </c>
+      <c r="R14" t="n">
+        <v>720</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>1586786552</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1586786552</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/대구_PT.xlsx
+++ b/naver-place-crawler/results_health/대구_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bbwellness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -628,10 +628,10 @@
         <v>113</v>
       </c>
       <c r="Q2" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="R2" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dnwls6050</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wannabefit2400</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q6" t="n">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="R6" t="n">
-        <v>2541</v>
+        <v>2544</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mollygym_vol.3/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="Q7" t="n">
         <v>546</v>
       </c>
       <c r="R7" t="n">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1348,39 +1348,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>클린짐 포레스트점 헬스&amp;P.T</t>
+          <t>TREX트레이닝센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hell12311@naver.com</t>
+          <t>trex211@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1399-4477</t>
+          <t>053-744-0405</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 수성구 용학로25안길 9 세종빌딩 2층</t>
+          <t>대구 수성구 동대구로 389 동방빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.youtube.com/channel/UCoIsLH8DW0KTkldy4KtyyEw</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1390,14 +1390,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4eysk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1409,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>252</v>
+        <v>61</v>
       </c>
       <c r="Q10" t="n">
-        <v>215</v>
+        <v>1138</v>
       </c>
       <c r="R10" t="n">
-        <v>467</v>
+        <v>1199</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1016045083</t>
+          <t>82375205</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016045083</t>
+          <t>https://m.place.naver.com/place/82375205</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,25 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>국민피티 월배점</t>
+          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kukminptwolbae@naver.com</t>
+          <t>atmhjqnib@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1341-2034</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
+          <t>대구 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kukminptwolbae</t>
+          <t>https://blog.naver.com/atmhjqnib</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1484,10 +1484,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdal64e</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>27</v>
+        <v>1196</v>
       </c>
       <c r="Q11" t="n">
-        <v>184</v>
+        <v>557</v>
       </c>
       <c r="R11" t="n">
-        <v>211</v>
+        <v>1753</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1009333460</t>
+          <t>671730517</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009333460</t>
+          <t>https://m.place.naver.com/place/671730517</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1531,34 +1535,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>헬핏 뉴로트레이닝 &amp; 재활PT 범어점</t>
+          <t>국민피티 월배점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>helfit@naver.com</t>
+          <t>kukminptwolbae@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1471-6364</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구 수성구 청호로95길 23 3층</t>
+          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/helfit</t>
+          <t>https://blog.naver.com/kukminptwolbae</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1578,14 +1578,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5sppd2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1597,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q12" t="n">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="R12" t="n">
-        <v>61</v>
+        <v>211</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,12 +1608,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1467150211</t>
+          <t>1009333460</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467150211</t>
+          <t>https://m.place.naver.com/place/1009333460</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1629,34 +1625,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 상인점</t>
+          <t>헬핏 뉴로트레이닝 &amp; 재활PT 범어점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>skyseung2@naver.com</t>
+          <t>helfit@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1469-7950</t>
+          <t>0507-1471-6364</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구 달서구 월곡로 219 4층</t>
+          <t>대구 수성구 청호로95길 23 3층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/helfit</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1666,12 +1662,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1681,7 +1677,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5i8k0</t>
+          <t>https://talk.naver.com/ct/w5sppd2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1695,13 +1691,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>964</v>
+        <v>21</v>
       </c>
       <c r="Q13" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="R13" t="n">
-        <v>1264</v>
+        <v>61</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1710,113 +1706,15 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1215597139</t>
+          <t>1467150211</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215597139</t>
+          <t>https://m.place.naver.com/place/1467150211</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>위즈고 헬스&amp;PT 시지점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>hanyang0226@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1305-6676</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>대구 수성구 신매로19길 56 4층 5층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wmrepxn</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>389</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>331</v>
-      </c>
-      <c r="R14" t="n">
-        <v>720</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1586786552</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1586786552</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/대구_PT.xlsx
+++ b/naver-place-crawler/results_health/대구_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="Q7" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="R7" t="n">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1618,41 +1618,41 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>헬핏 뉴로트레이닝 &amp; 재활PT 범어점</t>
+          <t>비무브짐24 헬스&amp;PT 상인점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>helfit@naver.com</t>
+          <t>skyseung2@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1471-6364</t>
+          <t>0507-1469-7950</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구 수성구 청호로95길 23 3층</t>
+          <t>대구 달서구 월곡로 219 4층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/helfit</t>
+          <t>https://blog.naver.com/skyseung2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5sppd2</t>
+          <t>https://talk.naver.com/ct/w5i8k0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1691,13 +1691,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>21</v>
+        <v>964</v>
       </c>
       <c r="Q13" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="R13" t="n">
-        <v>61</v>
+        <v>1264</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1706,17 +1706,115 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1467150211</t>
+          <t>1215597139</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467150211</t>
+          <t>https://m.place.naver.com/place/1215597139</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>위즈고 헬스&amp;PT 시지점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>woojung4545@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1305-6676</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>대구 수성구 신매로19길 56 4층 5층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/woojung4545</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmrepxn</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>389</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>332</v>
+      </c>
+      <c r="R14" t="n">
+        <v>721</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1586786552</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1586786552</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대구_PT.xlsx
+++ b/naver-place-crawler/results_health/대구_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -628,10 +628,10 @@
         <v>113</v>
       </c>
       <c r="Q2" t="n">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="R2" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>421</v>
       </c>
       <c r="Q6" t="n">
-        <v>2123</v>
+        <v>2128</v>
       </c>
       <c r="R6" t="n">
-        <v>2544</v>
+        <v>2549</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="Q7" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="R7" t="n">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="Q8" t="n">
         <v>180</v>
       </c>
       <c r="R8" t="n">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TREX트레이닝센터</t>
+          <t>클린짐 포레스트점 헬스&amp;P.T</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>trex211@naver.com</t>
+          <t>hell12311@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>053-744-0405</t>
+          <t>0507-1399-4477</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 수성구 동대구로 389 동방빌딩 3층</t>
+          <t>대구 수성구 용학로25안길 9 세종빌딩 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCoIsLH8DW0KTkldy4KtyyEw</t>
+          <t>https://youtube.com/@클린짐</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1390,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eysk</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>61</v>
+        <v>252</v>
       </c>
       <c r="Q10" t="n">
-        <v>1138</v>
+        <v>216</v>
       </c>
       <c r="R10" t="n">
-        <v>1199</v>
+        <v>468</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>82375205</t>
+          <t>1016045083</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/82375205</t>
+          <t>https://m.place.naver.com/place/1016045083</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="Q11" t="n">
         <v>557</v>
       </c>
       <c r="R11" t="n">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1715,104 +1719,6 @@
         </is>
       </c>
       <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>위즈고 헬스&amp;PT 시지점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>woojung4545@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1305-6676</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>대구 수성구 신매로19길 56 4층 5층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/woojung4545</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wmrepxn</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>389</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>332</v>
-      </c>
-      <c r="R14" t="n">
-        <v>721</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1586786552</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1586786552</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/대구_PT.xlsx
+++ b/naver-place-crawler/results_health/대구_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>비비웰니스 클럽 Wellness PT</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bbwellness@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1400-9891</t>
+          <t>0507-1356-4013</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구 중구 이천로 204-1 5층</t>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bbwellness</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sh6l</t>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="Q2" t="n">
-        <v>638</v>
+        <v>329</v>
       </c>
       <c r="R2" t="n">
-        <v>751</v>
+        <v>432</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1417211379</t>
+          <t>1701902663</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1417211379</t>
+          <t>https://m.place.naver.com/place/1701902663</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 대구점</t>
+          <t>워너비핏</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>l860923l@naver.com</t>
+          <t>wannabefit2400@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1356-4013</t>
+          <t>0507-1407-2402</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
+          <t>대구 수성구 달구벌대로 2317 . 105동 지하1층 비1호(수성동4 가, 우방사랑마을아파트)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems2</t>
+          <t>https://blog.naver.com/wannabefit2400</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r5eg</t>
+          <t>https://talk.naver.com/ct/w40ykq</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="Q3" t="n">
-        <v>329</v>
+        <v>123</v>
       </c>
       <c r="R3" t="n">
-        <v>432</v>
+        <v>249</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1701902663</t>
+          <t>1742130217</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701902663</t>
+          <t>https://m.place.naver.com/place/1742130217</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>플랜PT샵</t>
+          <t>커슬짐 헬스&amp;PT 봉덕점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dnwls6050@naver.com</t>
+          <t>almond_gym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1439-8242</t>
+          <t>0507-1332-7900</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 북구 학정로 430 3층 304 305호</t>
+          <t>대구 남구 대봉로 36 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dnwls6050</t>
+          <t>https://www.instagram.com/kusclegym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuz9732</t>
+          <t>https://talk.naver.com/ct/w4eizx</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="n">
-        <v>235</v>
+        <v>124</v>
       </c>
       <c r="R4" t="n">
-        <v>341</v>
+        <v>156</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,51 +836,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1053211445</t>
+          <t>1042608364</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053211445</t>
+          <t>https://m.place.naver.com/place/1042608364</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>워너비핏</t>
+          <t>커슬짐 헬스&amp;PT 중동점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wannabefit2400@naver.com</t>
+          <t>kuscles@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1407-2402</t>
+          <t>0507-1486-7445</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 수성구 달구벌대로 2317 . 105동 지하1층 비1호(수성동4 가, 우방사랑마을아파트)</t>
+          <t>대구 수성구 수성로 193 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wannabefit2400</t>
+          <t>https://www.instagram.com/kuscles</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ykq</t>
+          <t>https://talk.naver.com/ct/wbv5aq7</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="Q5" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="R5" t="n">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1742130217</t>
+          <t>1930053684</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742130217</t>
+          <t>https://m.place.naver.com/place/1930053684</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="Q8" t="n">
         <v>180</v>
       </c>
       <c r="R8" t="n">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="Q9" t="n">
         <v>1022</v>
       </c>
       <c r="R9" t="n">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1532,195 +1532,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>국민피티 월배점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>kukminptwolbae@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/kukminptwolbae</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>184</v>
-      </c>
-      <c r="R12" t="n">
-        <v>211</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1009333460</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1009333460</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>비무브짐24 헬스&amp;PT 상인점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>skyseung2@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1469-7950</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>대구 달서구 월곡로 219 4층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/skyseung2</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5i8k0</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>964</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>300</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1264</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1215597139</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1215597139</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
